--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5385</v>
+        <v>5477.96</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6079.94</v>
+        <v>6001.35</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3031.28</v>
+        <v>2992.77</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2677.55</v>
+        <v>2650.91</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1745.47</v>
+        <v>1741.69</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5683.58</v>
+        <v>5690.87</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3478.06</v>
+        <v>3478.08</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6962.08</v>
+        <v>7138.08</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3574.05</v>
+        <v>3561.32</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4431.05</v>
+        <v>4443.88</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>982.7</v>
+        <v>985.54</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1855.41</v>
+        <v>1845.31</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4867.8</v>
+        <v>4948.03</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>765.72</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6145.14</v>
+        <v>6066.03</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>974.7</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8660.92</v>
+        <v>8623.610000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>829.49</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2025.11</v>
+        <v>1970.89</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2895.84</v>
+        <v>2907.88</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7326.23</v>
+        <v>7388.4</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3210.52</v>
+        <v>3250.03</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8568.639999999999</v>
+        <v>8682.709999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1061.45</v>
+        <v>1065.47</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4409.28</v>
+        <v>4432.73</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>60664.03</v>
+        <v>59803.07</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>787.89</v>
+        <v>776.71</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2164.93</v>
+        <v>2135.18</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>63841.53</v>
+        <v>64447.96</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17062.61</v>
+        <v>16976.17</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4504.55</v>
+        <v>4432.33</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>782.61</v>
+        <v>773.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3390-366-CM25</t>
+          <t>3390-9-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5477.96</v>
+        <v>2787.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1415864-44-CM25</t>
+          <t>3390-11-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6001.35</v>
+        <v>1720.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3390-384-CM25</t>
+          <t>3390-13-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2992.77</v>
+        <v>837.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>720-1093-CM25</t>
+          <t>3390-14-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2650.91</v>
+        <v>1481.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>720-1104-CM25</t>
+          <t>3390-15-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1741.69</v>
+        <v>2511.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1079596-416-CM25</t>
+          <t>3390-29-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>INDUSTRIA DISTRIBUIDORA DE MERCADO SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>77.745.829-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5690.87</v>
+        <v>1646.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3390-3-CM26</t>
+          <t>3390-52-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SERVICIOS  CLIMATIKA LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.465.131-6</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3478.08</v>
+        <v>8276.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4232-8-CM26</t>
+          <t>3390-50-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7138.08</v>
+        <v>3741.06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3390-18-CM26</t>
+          <t>5702-143-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3561.32</v>
+        <v>784.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>720-7-CM26</t>
+          <t>5702-149-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4443.88</v>
+        <v>2921.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1317925-6-CM26</t>
+          <t>3390-74-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>SOCIEDAD DE INVERSIONES XONKET SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>77.176.545-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>985.54</v>
+        <v>2833.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3390-47-CM26</t>
+          <t>3390-105-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1845.31</v>
+        <v>1074.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4232-6-CM26</t>
+          <t>3390-121-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4948.03</v>
+        <v>1514.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4232-26-CM26</t>
+          <t>720-167-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>778.34</v>
+        <v>780.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2585-165-CM26</t>
+          <t>3390-142-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6066.03</v>
+        <v>1743.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3390-80-CM26</t>
+          <t>2585-3534-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>992.37</v>
+        <v>1902.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1110404-228-CM26</t>
+          <t>5358-133-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8623.610000000001</v>
+        <v>731.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>720-88-CM26</t>
+          <t>3390-172-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>803.04</v>
+        <v>2050.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5042-12-CM26</t>
+          <t>3390-159-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1970.89</v>
+        <v>3716.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3390-116-CM26</t>
+          <t>3390-198-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2907.88</v>
+        <v>3134.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2585-256-CM26</t>
+          <t>3390-196-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7388.4</v>
+        <v>2551.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5042-15-CM26</t>
+          <t>3390-197-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3250.03</v>
+        <v>5632.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1110404-319-CM26</t>
+          <t>720-235-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8682.709999999999</v>
+        <v>4377.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3390-165-CM26</t>
+          <t>3390-204-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1065.47</v>
+        <v>4383.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1058758-115-CM26</t>
+          <t>1110404-650-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4432.73</v>
+        <v>9502.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2585-223-CM26</t>
+          <t>1572-212-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>59803.07</v>
+        <v>13881.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>720-149-CM26</t>
+          <t>5042-19-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>776.71</v>
+        <v>4281.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4232-63-CM26</t>
+          <t>1774-114-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MAR DEL SUR SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>83.610.800-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2135.18</v>
+        <v>1204.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5750-48-CM26</t>
+          <t>1075963-22347-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>64447.96</v>
+        <v>6815.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2585-592-CM26</t>
+          <t>1236-130-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA WAY SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.532.399-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16976.17</v>
+        <v>727.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1572-78-CM26</t>
+          <t>4232-99-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4432.33</v>
+        <v>3648.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1774-91-CM26</t>
+          <t>720-370-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,6 +2460,2507 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
+        <v>799.1799999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2585-4177-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>4725.55</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>707409-103-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>798.45</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1110404-1293-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>7364.19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2585-4261-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1134.87</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1053139-205-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AIRE ACONDICIONADO LUIS SEBASTIAN VERGARA MARQUEZ E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.705.500-5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>5753.46</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1262-33-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>3827.33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1110404-1361-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>10766.17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3390-346-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>3003.23</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3390-347-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>956.6799999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3390-366-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>5477.96</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1415864-44-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.533.000-0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Instituto de Seguridad Laboral</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>6001.35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3390-384-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.579.703-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2992.77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>720-1093-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>2650.91</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>720-1104-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1741.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1079596-416-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>5690.87</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3390-3-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>INGENIERIA Y SERVICIOS  CLIMATIKA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.465.131-6</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>3478.08</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4232-8-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>7138.08</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3390-18-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3561.32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>720-7-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>4443.88</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1317925-6-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>985.54</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3390-47-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>1845.31</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4232-6-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>4948.03</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4232-26-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>778.34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2585-165-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>6066.03</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3390-80-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>992.37</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1110404-228-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>8623.610000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>720-88-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>803.04</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>5042-12-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1970.89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3390-116-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>2907.88</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2585-256-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>7388.4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>5042-15-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>77.610.398-5</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>3250.03</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1110404-319-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>62.000.660-2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SOSEG SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.897.534-5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>8682.709999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3390-165-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>1065.47</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1058758-115-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>4432.73</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2585-223-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>59803.07</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>720-149-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>776.71</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4232-63-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Arica</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>2135.18</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5750-48-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>64447.96</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2585-592-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>16976.17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1572-78-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>4432.33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1774-91-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.804.001-3</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
         <v>773.5</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2893,7 +2893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3390-346-CM25</t>
+          <t>3390-347-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3003.23</v>
+        <v>956.6799999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3390-347-CM25</t>
+          <t>3390-346-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>956.6799999999999</v>
+        <v>3003.23</v>
       </c>
     </row>
     <row r="43">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1415864-44-CM25</t>
+          <t>3390-384-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6001.35</v>
+        <v>2992.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3390-384-CM25</t>
+          <t>720-1093-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2992.77</v>
+        <v>2650.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>720-1093-CM25</t>
+          <t>720-1104-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2650.91</v>
+        <v>1741.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>720-1104-CM25</t>
+          <t>1079596-416-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1741.69</v>
+        <v>5690.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1079596-416-CM25</t>
+          <t>3390-3-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>INGENIERIA Y SERVICIOS  CLIMATIKA LIMITADA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.465.131-6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5690.87</v>
+        <v>3478.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3390-3-CM26</t>
+          <t>4232-8-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SERVICIOS  CLIMATIKA LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.465.131-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3478.08</v>
+        <v>7138.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4232-8-CM26</t>
+          <t>3390-18-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7138.08</v>
+        <v>3561.32</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3390-18-CM26</t>
+          <t>720-7-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3561.32</v>
+        <v>4443.88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>720-7-CM26</t>
+          <t>1317925-6-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4443.88</v>
+        <v>985.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1317925-6-CM26</t>
+          <t>3390-47-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>985.54</v>
+        <v>1845.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3390-47-CM26</t>
+          <t>4232-6-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1845.31</v>
+        <v>4948.03</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4232-6-CM26</t>
+          <t>4232-26-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4948.03</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4232-26-CM26</t>
+          <t>2585-165-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>778.34</v>
+        <v>6066.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2585-165-CM26</t>
+          <t>3390-80-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6066.03</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3390-80-CM26</t>
+          <t>1110404-228-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>992.37</v>
+        <v>8623.610000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1110404-228-CM26</t>
+          <t>720-88-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>8623.610000000001</v>
+        <v>803.04</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>720-88-CM26</t>
+          <t>5042-12-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>803.04</v>
+        <v>1970.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5042-12-CM26</t>
+          <t>3390-116-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1970.89</v>
+        <v>2907.88</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3390-116-CM26</t>
+          <t>2585-256-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2907.88</v>
+        <v>7388.4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2585-256-CM26</t>
+          <t>5042-15-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>77.610.398-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7388.4</v>
+        <v>3250.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5042-15-CM26</t>
+          <t>1110404-319-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VALDEBEBAS SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.610.398-5</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3250.03</v>
+        <v>8682.709999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1110404-319-CM26</t>
+          <t>3390-165-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8682.709999999999</v>
+        <v>1065.47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3390-165-CM26</t>
+          <t>1058758-115-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1065.47</v>
+        <v>4432.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1058758-115-CM26</t>
+          <t>2585-223-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>4432.73</v>
+        <v>59803.07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2585-223-CM26</t>
+          <t>720-149-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>59803.07</v>
+        <v>776.71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>720-149-CM26</t>
+          <t>4232-63-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>776.71</v>
+        <v>2135.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4232-63-CM26</t>
+          <t>5750-48-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2135.18</v>
+        <v>64447.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5750-48-CM26</t>
+          <t>2585-592-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>64447.96</v>
+        <v>16976.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2585-592-CM26</t>
+          <t>1572-78-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>16976.17</v>
+        <v>4432.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1572-78-CM26</t>
+          <t>1774-91-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.804.001-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4432.33</v>
+        <v>773.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1774-91-CM26</t>
+          <t>2369-111-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.804.001-3</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,7 +4961,617 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>773.5</v>
+        <v>37747.85</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2585-926-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>26911.42</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2585-950-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>7175.28</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>696027-57-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>2121.27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4232-85-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.505.101-4</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>1953.85</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5360-233-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>5119.02</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2366-505-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>29861.04</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>5750-74-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>73632.58</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2585-1074-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>31151.38</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5042-40-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EASY RETAIL S.A. .-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.568.660-1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>10040.41</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5042-41-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EASY RETAIL S.A. .-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.568.660-1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>7950.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -867,7 +867,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1481,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1668,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2343,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2530,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2595,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2721,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2969,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3034,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3465,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3652,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3839,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4209,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4335,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4583,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4709,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4957,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5022,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5087,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5152,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5217,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5282,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5347,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -2160,7 +2160,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5429,7 +5429,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5750-74-CM26</t>
+          <t>3348-103-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5469,28 +5469,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>73632.58</v>
+        <v>4906.16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2585-1074-CM26</t>
+          <t>5750-74-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5505,22 +5509,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5530,12 +5534,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5545,13 +5549,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>31151.38</v>
+        <v>73632.58</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5042-40-CM26</t>
+          <t>2585-1074-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5566,7 +5570,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5591,12 +5595,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>EASY RETAIL S.A. .-</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.568.660-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5606,13 +5610,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10040.41</v>
+        <v>31151.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5042-41-CM26</t>
+          <t>5042-40-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5667,6 +5671,67 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
+        <v>10040.41</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>5042-41-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EASY RETAIL S.A. .-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.568.660-1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
         <v>7950.84</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/arica-y-parinacota.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
